--- a/sources/metaPee/combined/subexposure_views/no/Plot/exposures_meta_analysis_papillary_renal_cell_carcinoma_combined.xlsx
+++ b/sources/metaPee/combined/subexposure_views/no/Plot/exposures_meta_analysis_papillary_renal_cell_carcinoma_combined.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,11 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -501,8 +508,39 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>alcohol</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr"/>
+      <c r="H2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="2" t="n">
+        <v>120852</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:K2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
